--- a/src/test/resources/ImportTemplate/Pushdown - Redshift.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown - Redshift.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADB73D7-F86F-4E46-A661-91DFB5B188D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4257032C-B9B9-4C59-9D0F-62B17A04E43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <t>select * from icedqrs.regression_database.reg_employee</t>
   </si>
   <si>
-    <t>Pushdown_ImportSQL--Redshift--RegEmployee_table</t>
+    <t>Pushdown_ImportSQL--CDW-Redshift_RegEmployee</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Pushdown - Redshift.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown - Redshift.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4257032C-B9B9-4C59-9D0F-62B17A04E43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C981B2-75EE-4357-9D47-49826D3804B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <t>select * from icedqrs.regression_database.reg_employee</t>
   </si>
   <si>
-    <t>Pushdown_ImportSQL--CDW-Redshift_RegEmployee</t>
+    <t>Pushdown_ImportSQL__CDW_Redshift_RegEmployee</t>
   </si>
 </sst>
 </file>
